--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Åsa Tengström</t>
+          <t>Åsa Tengström, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1026,7 +1026,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åsa Tengström, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,6 +718,9 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråknäbben sydväst, Vrm</t>
@@ -773,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Åsa Tengström</t>
+          <t>Elvira Ljungberg, Åsa Tengström, Caroline Ahlgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -910,7 +914,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1030,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1146,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1262,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1378,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1494,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1610,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1726,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1842,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Åsa Tengström, Caroline Ahlgren</t>
+          <t>Åsa Tengström, Elvira Ljungberg, Caroline Ahlgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Tengström, Elvira Ljungberg, Caroline Ahlgren</t>
+          <t>Elvira Ljungberg, Åsa Tengström, Caroline Ahlgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
